--- a/ClaudeCode/qa/指摘事項一覧_詳細設計_20260301.xlsx
+++ b/ClaudeCode/qa/指摘事項一覧_詳細設計_20260301.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\CREATE\ADAMSLite\ClaudeCode\qa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2681EAE-080A-490A-8C0C-22E0AD2910B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFDF9DF-F7C0-41F0-ACBC-471C59290BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="指摘事項一覧_ADAMSLite" sheetId="1" r:id="rId1"/>
+    <sheet name="指摘事項一覧_詳細設計_20260301" sheetId="1" r:id="rId1"/>
     <sheet name="凡例" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">指摘事項一覧_ADAMSLite!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">指摘事項一覧_詳細設計_20260301!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
